--- a/self-rag/documents/ApplicationLog.xlsx
+++ b/self-rag/documents/ApplicationLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sajal\Project\Agentic AI\self-rag\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FC5080-49F3-4B8C-BF80-511DA8F93C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B53066-C1F3-43D0-9C58-F9F7E215741D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -543,8 +543,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -993,7 +996,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -1006,7 +1009,7 @@
       <c r="D9" t="s">
         <v>8</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1078,7 +1081,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -1091,7 +1094,7 @@
       <c r="D14" t="s">
         <v>29</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1163,7 +1166,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -1176,7 +1179,7 @@
       <c r="D19" t="s">
         <v>11</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="1" t="s">
         <v>36</v>
       </c>
     </row>
